--- a/DIRECCIONES_CENTROS.xlsx
+++ b/DIRECCIONES_CENTROS.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://argiafundazioa.sharepoint.com/sites/ARGIA/Documentos compartidos/PROCESOS/P08 KUDEAKETA ADMINISTRATIBOA/01. GESTION/GABRIEL/FORMACIÓN/HUELLA DE CARBONO/2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://argiafundazioa.sharepoint.com/sites/ARGIA/Documentos compartidos/PROCESOS/P08 KUDEAKETA ADMINISTRATIBOA/01. GESTION/GABRIEL/PYTHON/PILOTOS/ARGIA_APPS/KM HUELLA CARBONO/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="11_61E7E7CD87452E2E2BE2D4CA3AC3B219CC253533" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{339A83F5-13F2-4DAA-9CC7-B59B51A1C756}"/>
+  <xr:revisionPtr revIDLastSave="33" documentId="11_61E7E7CD87452E2E2BE2D4CA3AC3B219CC253533" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6C0FD4EB-2F2F-49DA-8245-999E9079C5D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
   <si>
     <t xml:space="preserve">CENTRO </t>
   </si>
@@ -54,64 +54,70 @@
     <t>VIVIENDAS BILBAO/SONDIKA</t>
   </si>
   <si>
-    <t>CALLE</t>
-  </si>
-  <si>
-    <t>NUMERO</t>
-  </si>
-  <si>
-    <t>MUNICIPIO</t>
-  </si>
-  <si>
-    <t>COD_POSTAL</t>
-  </si>
-  <si>
-    <t>TRINIDAD</t>
-  </si>
-  <si>
-    <t>GETXO</t>
-  </si>
-  <si>
-    <t>GALDAMES</t>
-  </si>
-  <si>
-    <t>Zubiaga Auzoa</t>
-  </si>
-  <si>
-    <t>AGIRRE LEHENDAKARI</t>
-  </si>
-  <si>
-    <t>BERANGO</t>
-  </si>
-  <si>
-    <t>GORDEXOLA</t>
-  </si>
-  <si>
-    <t>GABRIEL ARESTI</t>
-  </si>
-  <si>
-    <t>BILBAO</t>
-  </si>
-  <si>
-    <t>CALLE MAYOR</t>
-  </si>
-  <si>
-    <t>SAN VICENTE DE BARAKALDO</t>
-  </si>
-  <si>
-    <t>BARAKALDO</t>
-  </si>
-  <si>
-    <t>FEDERICO MOYÚA PLAZA</t>
-  </si>
-  <si>
     <t>CLUB SOCIAL</t>
   </si>
   <si>
-    <t>GAZTELUMENDI</t>
-  </si>
-  <si>
     <t>HOSPITAL DE DÍA</t>
+  </si>
+  <si>
+    <t>43.35594185537243, -3.008112498487399</t>
+  </si>
+  <si>
+    <t>COORDENADAS</t>
+  </si>
+  <si>
+    <t>43.353471689073444, -3.012483816632963</t>
+  </si>
+  <si>
+    <t>43.36298207152071, -2.9934568608137635</t>
+  </si>
+  <si>
+    <t>DIRECCION COMPLETA</t>
+  </si>
+  <si>
+    <t>Agirre Lehendakariaren Kalea, 5, 48640 Baserri-Santa Ana, Bizkaia</t>
+  </si>
+  <si>
+    <t>Trinidad Kalea, 11, 48993 Algorta, Bizkaia</t>
+  </si>
+  <si>
+    <t>Bo. Zubiaga, 3, 48191 San Pedro Galdames, Biscay</t>
+  </si>
+  <si>
+    <t>43.252693855496226, -3.099219660819548</t>
+  </si>
+  <si>
+    <t>Zubiete Auzoa, 1, 48192 Zubiete, Biscay</t>
+  </si>
+  <si>
+    <t>43.18034564750491, -3.0717286031508397</t>
+  </si>
+  <si>
+    <t>Gabriel Aresti Hiribidea, 11, Otxarkoaga - Txurdinaga, 48004 Bilbao, Bizkaia</t>
+  </si>
+  <si>
+    <t>43.25777780232809, -2.9077942136460515</t>
+  </si>
+  <si>
+    <t>Mayor Kalea, 22, 48930 Areeta / Las Arenas, Bizkaia</t>
+  </si>
+  <si>
+    <t>43.326524266667874, -3.0120585611418385</t>
+  </si>
+  <si>
+    <t>48901 San Vicente de Barakaldo, Biscay</t>
+  </si>
+  <si>
+    <t>43.2962920985631, -2.9892168958196876</t>
+  </si>
+  <si>
+    <t>Federico Moyúa Plaza, 2, Abando, 48009 Bilbao, Bizkaia</t>
+  </si>
+  <si>
+    <t>43.26260362890993, -2.934917929400865</t>
+  </si>
+  <si>
+    <t>Gaztelumendi Kalea, 30, 48991 Algorta, Bizkaia</t>
   </si>
 </sst>
 </file>
@@ -170,7 +176,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -183,6 +189,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -463,184 +472,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="29" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="54.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="29.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="63.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>11</v>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C2" s="2">
-        <v>11</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2">
-        <v>48993</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2">
-        <v>3</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="2">
-        <v>48191</v>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="2">
-        <v>5</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2">
-        <v>48640</v>
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2">
-        <v>48192</v>
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="2">
-        <v>11</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="2">
-        <v>48004</v>
+        <v>21</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="2">
-        <v>22</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="2">
-        <v>48930</v>
+        <v>23</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E8" s="2">
-        <v>48901</v>
+        <v>25</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="2">
-        <v>2</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="2">
-        <v>48009</v>
+        <v>27</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="5">
-        <v>30</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" s="5">
-        <v>48991</v>
+        <v>29</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -658,6 +605,17 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="1d5091a6-487f-4efc-963e-2719c1a1abbf" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e8caff8-d6c5-4bf0-a687-685e2f20a773">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100EA6513C44DFE3D44A38D62D5C686422D" ma:contentTypeVersion="20" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="c3faea35e3afcb9e863de00d00ca0073">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="2e8caff8-d6c5-4bf0-a687-685e2f20a773" xmlns:ns3="1d5091a6-487f-4efc-963e-2719c1a1abbf" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="72faea73bb8c5644087581f544b61028" ns2:_="" ns3:_="">
     <xsd:import namespace="2e8caff8-d6c5-4bf0-a687-685e2f20a773"/>
@@ -912,17 +870,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="1d5091a6-487f-4efc-963e-2719c1a1abbf" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="2e8caff8-d6c5-4bf0-a687-685e2f20a773">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5C4A3420-D452-46DE-AFF3-1C423F8603CE}">
   <ds:schemaRefs>
@@ -932,6 +879,17 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62848B23-3CEA-4091-83B8-FAE8B9811166}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="1d5091a6-487f-4efc-963e-2719c1a1abbf"/>
+    <ds:schemaRef ds:uri="2e8caff8-d6c5-4bf0-a687-685e2f20a773"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D02D2912-1E7C-4036-8824-D693E7FA685A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -948,15 +906,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{62848B23-3CEA-4091-83B8-FAE8B9811166}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="1d5091a6-487f-4efc-963e-2719c1a1abbf"/>
-    <ds:schemaRef ds:uri="2e8caff8-d6c5-4bf0-a687-685e2f20a773"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>